--- a/AC_2014/3-Karimnagar_7_031.xlsx
+++ b/AC_2014/3-Karimnagar_7_031.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -106,11 +111,33 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,6 +172,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -15687,191 +15723,192 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="7" t="inlineStr">
+      <c r="A279" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B279" s="8" t="inlineStr"/>
-      <c r="C279" s="9">
+      <c r="B279" s="11" t="inlineStr"/>
+      <c r="C279" s="19">
         <f>SUM(C6:C278)</f>
         <v/>
       </c>
-      <c r="D279" s="9">
+      <c r="D279" s="19">
         <f>SUM(D6:D278)</f>
         <v/>
       </c>
-      <c r="E279" s="9">
+      <c r="E279" s="19">
         <f>SUM(E6:E278)</f>
         <v/>
       </c>
-      <c r="F279" s="9">
+      <c r="F279" s="19">
         <f>SUM(F6:F278)</f>
         <v/>
       </c>
-      <c r="G279" s="9">
+      <c r="G279" s="19">
         <f>SUM(G6:G278)</f>
         <v/>
       </c>
-      <c r="H279" s="9">
+      <c r="H279" s="19">
         <f>SUM(H6:H278)</f>
         <v/>
       </c>
-      <c r="I279" s="9">
+      <c r="I279" s="19">
         <f>SUM(I6:I278)</f>
         <v/>
       </c>
-      <c r="J279" s="9">
+      <c r="J279" s="19">
         <f>SUM(J6:J278)</f>
         <v/>
       </c>
-      <c r="K279" s="9">
+      <c r="K279" s="19">
         <f>SUM(K6:K278)</f>
         <v/>
       </c>
-      <c r="L279" s="9">
+      <c r="L279" s="19">
         <f>SUM(L6:L278)</f>
         <v/>
       </c>
-      <c r="M279" s="9">
+      <c r="M279" s="19">
         <f>SUM(M6:M278)</f>
         <v/>
       </c>
-      <c r="N279" s="9">
+      <c r="N279" s="19">
         <f>SUM(N6:N278)</f>
         <v/>
       </c>
-      <c r="O279" s="9">
+      <c r="O279" s="19">
         <f>SUM(O6:O278)</f>
         <v/>
       </c>
-      <c r="P279" s="9">
+      <c r="P279" s="19">
         <f>SUM(P6:P278)</f>
         <v/>
       </c>
-      <c r="Q279" s="9">
+      <c r="Q279" s="19">
         <f>SUM(Q6:Q278)</f>
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="10" t="inlineStr">
+      <c r="A280" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B280" s="11" t="inlineStr"/>
-      <c r="C280" s="12" t="n">
+      <c r="C280" s="19" t="n">
         <v>623</v>
       </c>
-      <c r="D280" s="12" t="n">
+      <c r="D280" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="E280" s="12" t="n">
+      <c r="E280" s="19" t="n">
         <v>222</v>
       </c>
-      <c r="F280" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G280" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I280" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J280" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K280" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L280" s="12" t="n">
+      <c r="F280" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K280" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" s="19" t="n">
         <v>863</v>
       </c>
-      <c r="M280" s="12" t="n">
+      <c r="M280" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="N280" s="12" t="n">
+      <c r="N280" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="O280" s="12" t="n">
+      <c r="O280" s="19" t="n">
         <v>893</v>
       </c>
-      <c r="P280" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q280" s="13" t="n">
+      <c r="P280" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="14" t="inlineStr">
+      <c r="A281" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B281" s="15" t="inlineStr"/>
-      <c r="C281" s="16">
+      <c r="B281" s="11" t="inlineStr"/>
+      <c r="C281" s="20">
         <f>C279+C280</f>
         <v/>
       </c>
-      <c r="D281" s="16">
+      <c r="D281" s="20">
         <f>D279+D280</f>
         <v/>
       </c>
-      <c r="E281" s="16">
+      <c r="E281" s="20">
         <f>E279+E280</f>
         <v/>
       </c>
-      <c r="F281" s="16">
+      <c r="F281" s="20">
         <f>F279+F280</f>
         <v/>
       </c>
-      <c r="G281" s="16">
+      <c r="G281" s="20">
         <f>G279+G280</f>
         <v/>
       </c>
-      <c r="H281" s="16">
+      <c r="H281" s="20">
         <f>H279+H280</f>
         <v/>
       </c>
-      <c r="I281" s="16">
+      <c r="I281" s="20">
         <f>I279+I280</f>
         <v/>
       </c>
-      <c r="J281" s="16">
+      <c r="J281" s="20">
         <f>J279+J280</f>
         <v/>
       </c>
-      <c r="K281" s="16">
+      <c r="K281" s="20">
         <f>K279+K280</f>
         <v/>
       </c>
-      <c r="L281" s="16">
+      <c r="L281" s="20">
         <f>L279+L280</f>
         <v/>
       </c>
-      <c r="M281" s="16">
+      <c r="M281" s="20">
         <f>M279+M280</f>
         <v/>
       </c>
-      <c r="N281" s="16">
+      <c r="N281" s="20">
         <f>N279+N280</f>
         <v/>
       </c>
-      <c r="O281" s="16">
+      <c r="O281" s="20">
         <f>O279+O280</f>
         <v/>
       </c>
-      <c r="P281" s="16">
+      <c r="P281" s="20">
         <f>P279+P280</f>
         <v/>
       </c>
-      <c r="Q281" s="17" t="n">
-        <v>0</v>
+      <c r="Q281" s="20">
+        <f>Q279+Q280</f>
+        <v/>
       </c>
     </row>
   </sheetData>
